--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
@@ -8001,7 +8001,7 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-001</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-002</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-003</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-004</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-004</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-005</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-006</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-006</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-006</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-007</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-008</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-009</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">

--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_libLogEncrypt_20260917.xlsx
@@ -8001,7 +8001,7 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
